--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$90</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$98</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$82</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4145,7 +4145,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 26.1, "op_wape_pct": 27.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 569.88, "rev_act": 814.15, "op_pred": 76.42, "op_act": 115.69}, {"q": "2025Q4", "rev_pred": 610.49, "rev_act": 806.0, "op_pred": 81.87, "op_act": 121.05}, {"q": "2026Q1", "rev_pred": 578.02, "rev_act": 822.75, "op_pred": 77.51, "op_act": 93.5}, {"q": "2026Q2", "rev_pred": 667.36, "rev_act": 837.46, "op_pred": 89.49, "op_act": 72.12}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 26.1, "op_wape_pct": 27.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 569.88, "rev_act": 814.15, "op_pred": 76.42, "op_act": 115.69}, {"q": "2025Q4", "rev_pred": 610.49, "rev_act": 806.0, "op_pred": 81.87, "op_act": 121.05}, {"q": "2026Q1", "rev_pred": 578.02, "rev_act": 822.75, "op_pred": 77.51, "op_act": 93.5}, {"q": "2026Q2", "rev_pred": 667.36, "rev_act": 837.46, "op_pred": 89.49, "op_act": 72.12}]}</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO90"/>
+  <dimension ref="A1:AO98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16038,78 +16038,33 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>5631.88</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F73" s="9" t="n"/>
-      <c r="G73" s="18" t="n">
-        <v>1308.85</v>
-      </c>
-      <c r="H73" s="18" t="n">
-        <v>7559.13</v>
-      </c>
-      <c r="I73" s="18" t="n">
-        <v>19713.69</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>17724.36</v>
-      </c>
-      <c r="K73" s="34" t="n">
-        <v>46306.03</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>8744.18</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>17711.67</v>
-      </c>
-      <c r="N73" s="18" t="n">
-        <v>18769.41</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>9110.219999999999</v>
-      </c>
-      <c r="P73" s="34" t="n">
-        <v>54335.48</v>
-      </c>
-      <c r="Q73" s="18" t="n">
-        <v>30487.9</v>
-      </c>
-      <c r="R73" s="18" t="n">
-        <v>7843.26</v>
-      </c>
-      <c r="S73" s="18" t="n">
-        <v>8998.17</v>
-      </c>
-      <c r="T73" s="18" t="n">
-        <v>11905.71</v>
-      </c>
-      <c r="U73" s="34" t="n">
-        <v>59235.04</v>
-      </c>
+      <c r="K73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="U73" s="9" t="n"/>
       <c r="V73" s="18" t="n">
-        <v>12123.88</v>
+        <v>1109.68</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>-4130.61</v>
+        <v>1068.14</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>3252.87</v>
+        <v>896.13</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>8119.54</v>
+        <v>622.78</v>
       </c>
       <c r="Z73" s="34" t="n">
-        <v>19365.68</v>
+        <v>3696.73</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>15166.52</v>
+        <v>528.01</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>23690.2</v>
+        <v>853.8200000000001</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -16131,78 +16086,33 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>-14.38</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F74" s="9" t="n"/>
-      <c r="G74" s="18" t="n">
-        <v>-1143.05</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>-1450.86</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>-1331.31</v>
-      </c>
-      <c r="J74" s="18" t="n">
-        <v>-50.52</v>
-      </c>
-      <c r="K74" s="34" t="n">
-        <v>-3975.74</v>
-      </c>
-      <c r="L74" s="18" t="n">
-        <v>-4298.49</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>-4579.57</v>
-      </c>
-      <c r="N74" s="18" t="n">
-        <v>-2458.53</v>
-      </c>
-      <c r="O74" s="18" t="n">
-        <v>-2257.13</v>
-      </c>
-      <c r="P74" s="34" t="n">
-        <v>-13593.72</v>
-      </c>
-      <c r="Q74" s="18" t="n">
-        <v>-33.48</v>
-      </c>
-      <c r="R74" s="18" t="n">
-        <v>-8200.08</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>-3112.13</v>
-      </c>
-      <c r="T74" s="18" t="n">
-        <v>-3147.12</v>
-      </c>
-      <c r="U74" s="34" t="n">
-        <v>-14492.81</v>
-      </c>
+      <c r="K74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
       <c r="V74" s="18" t="n">
-        <v>-1958.87</v>
+        <v>1143</v>
       </c>
       <c r="W74" s="18" t="n">
-        <v>-2800.01</v>
+        <v>1996.34</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>-1806.14</v>
+        <v>1572.58</v>
       </c>
       <c r="Y74" s="18" t="n">
-        <v>-4762.65</v>
+        <v>1539.32</v>
       </c>
       <c r="Z74" s="34" t="n">
-        <v>-11327.67</v>
+        <v>6251.24</v>
       </c>
       <c r="AA74" s="18" t="n">
-        <v>-3404.59</v>
+        <v>8560.67</v>
       </c>
       <c r="AB74" s="19" t="n">
-        <v>-3446.91</v>
+        <v>13138.22</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -16224,78 +16134,33 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>-4821.21</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="18" t="n">
-        <v>-9050.98</v>
-      </c>
-      <c r="H75" s="18" t="n">
-        <v>-7501.76</v>
-      </c>
-      <c r="I75" s="18" t="n">
-        <v>-23861.58</v>
-      </c>
-      <c r="J75" s="18" t="n">
-        <v>-22154.8</v>
-      </c>
-      <c r="K75" s="34" t="n">
-        <v>-62569.12</v>
-      </c>
-      <c r="L75" s="18" t="n">
-        <v>-18693.6</v>
-      </c>
-      <c r="M75" s="18" t="n">
-        <v>-10389.25</v>
-      </c>
-      <c r="N75" s="18" t="n">
-        <v>-31607.3</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>-2384.59</v>
-      </c>
-      <c r="P75" s="34" t="n">
-        <v>-63074.74</v>
-      </c>
-      <c r="Q75" s="18" t="n">
-        <v>-7862.3</v>
-      </c>
-      <c r="R75" s="18" t="n">
-        <v>-22384.81</v>
-      </c>
-      <c r="S75" s="18" t="n">
-        <v>2712.94</v>
-      </c>
-      <c r="T75" s="18" t="n">
-        <v>-18234.75</v>
-      </c>
-      <c r="U75" s="34" t="n">
-        <v>-45768.92</v>
-      </c>
+      <c r="K75" s="9" t="n"/>
+      <c r="P75" s="9" t="n"/>
+      <c r="U75" s="9" t="n"/>
       <c r="V75" s="18" t="n">
-        <v>-8948.629999999999</v>
+        <v>156.64</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>6042.23</v>
+        <v>144.95</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>6871.48</v>
+        <v>148.26</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>-2917.41</v>
+        <v>148.88</v>
       </c>
       <c r="Z75" s="34" t="n">
-        <v>1047.67</v>
+        <v>598.73</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>-7548.33</v>
+        <v>151.66</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>-3526.6</v>
+        <v>153.64</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -16317,73 +16182,33 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>218.08</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="G76" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>183.33</v>
-      </c>
       <c r="K76" s="9" t="n"/>
-      <c r="L76" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="M76" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P76" s="34" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="R76" s="18" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="S76" s="18" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="T76" s="18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U76" s="34" t="n">
-        <v>62.93</v>
-      </c>
+      <c r="P76" s="9" t="n"/>
+      <c r="U76" s="9" t="n"/>
       <c r="V76" s="18" t="n">
-        <v>34.55</v>
+        <v>371.65</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>65.51000000000001</v>
+        <v>483.76</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>3.4</v>
+        <v>660.52</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>0</v>
+        <v>2118.01</v>
       </c>
       <c r="Z76" s="34" t="n">
-        <v>103.46</v>
+        <v>3633.94</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>17.19</v>
+        <v>1706.57</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>49.23</v>
+        <v>1905.71</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -16405,78 +16230,33 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>21.76</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
-      <c r="G77" s="18" t="n">
-        <v>1478.05</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>3027</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>867.86</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>1824.02</v>
-      </c>
-      <c r="K77" s="34" t="n">
-        <v>7196.93</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>2952.28</v>
-      </c>
-      <c r="M77" s="18" t="n">
-        <v>5562.44</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>6195.16</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>5569.21</v>
-      </c>
-      <c r="P77" s="34" t="n">
-        <v>20279.09</v>
-      </c>
-      <c r="Q77" s="18" t="n">
-        <v>3225.73</v>
-      </c>
-      <c r="R77" s="18" t="n">
-        <v>2368.39</v>
-      </c>
-      <c r="S77" s="18" t="n">
-        <v>3537</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>4178.41</v>
-      </c>
-      <c r="U77" s="34" t="n">
-        <v>13309.53</v>
-      </c>
+      <c r="K77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="U77" s="9" t="n"/>
       <c r="V77" s="18" t="n">
-        <v>4577.35</v>
+        <v>702.1799999999999</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>4107.83</v>
+        <v>1284.27</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>3738.06</v>
+        <v>920.1</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>2183.45</v>
+        <v>516.37</v>
       </c>
       <c r="Z77" s="34" t="n">
-        <v>14606.69</v>
+        <v>3422.92</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>1423.82</v>
+        <v>436.52</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>799.4299999999999</v>
+        <v>478.36</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -16498,47 +16278,34 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>36</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>24</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>40.5</v>
-      </c>
       <c r="K78" s="9" t="n"/>
-      <c r="L78" s="18" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="P78" s="9" t="n"/>
       <c r="U78" s="9" t="n"/>
-      <c r="Z78" s="9" t="n"/>
-      <c r="AB78" s="5" t="n"/>
+      <c r="V78" s="18" t="n">
+        <v>699.77</v>
+      </c>
+      <c r="W78" s="18" t="n">
+        <v>-68.48</v>
+      </c>
+      <c r="X78" s="18" t="n">
+        <v>440.43</v>
+      </c>
+      <c r="Y78" s="18" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="Z78" s="34" t="n">
+        <v>1171.99</v>
+      </c>
+      <c r="AA78" s="18" t="n">
+        <v>2804.1</v>
+      </c>
+      <c r="AB78" s="19" t="n">
+        <v>293.97</v>
+      </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
       <c r="AE78" s="11" t="n"/>
@@ -16559,78 +16326,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>-1351.47</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>-424.8</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>-1645.65</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>28642.64</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>-3846.38</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>22725.81</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>-291</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>-4749.92</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>-333.15</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>-2157.11</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>-7531.18</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>-1353.79</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>-9374.719999999999</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>-416.38</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>-1384.92</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>-12529.81</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
       <c r="V79" s="18" t="n">
-        <v>-455.2</v>
+        <v>108.74</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>-6925.51</v>
+        <v>3043.05</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>-7838.35</v>
+        <v>-2108.69</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>-1504.48</v>
+        <v>-129.72</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>-16723.54</v>
+        <v>913.38</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>-495.43</v>
+        <v>301.88</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>-13109.61</v>
+        <v>-33.85</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -16652,30 +16374,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>0</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>181.42</v>
-      </c>
       <c r="K80" s="9" t="n"/>
-      <c r="N80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
-      <c r="Z80" s="9" t="n"/>
-      <c r="AB80" s="5" t="n"/>
+      <c r="V80" s="18" t="n">
+        <v>953.04</v>
+      </c>
+      <c r="W80" s="18" t="n">
+        <v>923.1900000000001</v>
+      </c>
+      <c r="X80" s="18" t="n">
+        <v>747.87</v>
+      </c>
+      <c r="Y80" s="18" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="Z80" s="34" t="n">
+        <v>3098</v>
+      </c>
+      <c r="AA80" s="18" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="AB80" s="19" t="n">
+        <v>700.1799999999999</v>
+      </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -16696,42 +16422,79 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0</v>
+        <v>5631.88</v>
       </c>
       <c r="F81" s="9" t="n"/>
+      <c r="G81" s="18" t="n">
+        <v>1308.85</v>
+      </c>
+      <c r="H81" s="18" t="n">
+        <v>7559.13</v>
+      </c>
       <c r="I81" s="18" t="n">
-        <v>0</v>
+        <v>19713.69</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="n"/>
+        <v>17724.36</v>
+      </c>
+      <c r="K81" s="34" t="n">
+        <v>46306.03</v>
+      </c>
+      <c r="L81" s="18" t="n">
+        <v>8744.18</v>
+      </c>
+      <c r="M81" s="18" t="n">
+        <v>17711.67</v>
+      </c>
       <c r="N81" s="18" t="n">
-        <v>0</v>
+        <v>18769.41</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="9" t="n"/>
+        <v>9110.219999999999</v>
+      </c>
+      <c r="P81" s="34" t="n">
+        <v>54335.48</v>
+      </c>
+      <c r="Q81" s="18" t="n">
+        <v>30487.9</v>
+      </c>
+      <c r="R81" s="18" t="n">
+        <v>7843.26</v>
+      </c>
       <c r="S81" s="18" t="n">
-        <v>0</v>
+        <v>8998.17</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="9" t="n"/>
+        <v>11905.71</v>
+      </c>
+      <c r="U81" s="34" t="n">
+        <v>59235.04</v>
+      </c>
+      <c r="V81" s="18" t="n">
+        <v>12123.88</v>
+      </c>
+      <c r="W81" s="18" t="n">
+        <v>-4130.61</v>
+      </c>
       <c r="X81" s="18" t="n">
-        <v>7372.16</v>
+        <v>3252.87</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+        <v>8119.54</v>
+      </c>
+      <c r="Z81" s="34" t="n">
+        <v>19365.68</v>
+      </c>
+      <c r="AA81" s="18" t="n">
+        <v>15166.52</v>
+      </c>
+      <c r="AB81" s="19" t="n">
+        <v>23690.2</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -16752,78 +16515,78 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>-1636.57</v>
+        <v>-14.38</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>-16406.27</v>
+        <v>-1143.05</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>-2846.87</v>
+        <v>-1450.86</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>49325.89</v>
+        <v>-1331.31</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>-18521.09</v>
+        <v>-50.52</v>
       </c>
       <c r="K82" s="34" t="n">
-        <v>11551.66</v>
+        <v>-3975.74</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>-20317.01</v>
+        <v>-4298.49</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>5055.22</v>
+        <v>-4579.57</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>-26298.31</v>
+        <v>-2458.53</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>8933.99</v>
+        <v>-2257.13</v>
       </c>
       <c r="P82" s="34" t="n">
-        <v>-32626.11</v>
+        <v>-13593.72</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>42695.19</v>
+        <v>-33.48</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>-47790.68</v>
+        <v>-8200.08</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>13696.15</v>
+        <v>-3112.13</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>-7411.07</v>
+        <v>-3147.12</v>
       </c>
       <c r="U82" s="34" t="n">
-        <v>1189.59</v>
+        <v>-14492.81</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>2744.21</v>
+        <v>-1958.87</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-5207.97</v>
+        <v>-2800.01</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>2378.55</v>
+        <v>-1806.14</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>3619.03</v>
+        <v>-4762.65</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>3533.82</v>
+        <v>-11327.67</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>7392.62</v>
+        <v>-3404.59</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>7159</v>
+        <v>-3446.91</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16845,78 +16608,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>-9182.83</v>
+        <v>-4821.21</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>33900.03</v>
+        <v>-9050.98</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>-1258.59</v>
+        <v>-7501.76</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>24831.14</v>
+        <v>-23861.58</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>-10244.28</v>
+        <v>-22154.8</v>
       </c>
       <c r="K83" s="34" t="n">
-        <v>47228.3</v>
+        <v>-62569.12</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>37151.72</v>
+        <v>-18693.6</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>2482.7</v>
+        <v>-10389.25</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>-13127.26</v>
+        <v>-31607.3</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>4365.47</v>
+        <v>-2384.59</v>
       </c>
       <c r="P83" s="34" t="n">
-        <v>30872.63</v>
+        <v>-63074.74</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>52296.02</v>
+        <v>-7862.3</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>-23874.41</v>
+        <v>-22384.81</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>11051.68</v>
+        <v>2712.94</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>-7411.07</v>
+        <v>-18234.75</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>32062.22</v>
+        <v>-45768.92</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>34806.43</v>
+        <v>-8948.629999999999</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>-5207.97</v>
+        <v>6042.23</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>2378.55</v>
+        <v>6871.48</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>3619.03</v>
+        <v>-2917.41</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>35596.04</v>
+        <v>1047.67</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>42988.67</v>
+        <v>-7548.33</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>7158.99</v>
+        <v>-3526.6</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16938,75 +16701,73 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>218.08</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>1454.05</v>
+        <v>3</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>3027</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>827.36</v>
+        <v>48.41</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>1837.62</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>7146.03</v>
-      </c>
+        <v>183.33</v>
+      </c>
+      <c r="K84" s="9" t="n"/>
       <c r="L84" s="18" t="n">
-        <v>2933.38</v>
+        <v>30</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>5511.04</v>
+        <v>2</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>6195.16</v>
+        <v>22.19</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>5569.21</v>
+        <v>4.8</v>
       </c>
       <c r="P84" s="34" t="n">
-        <v>20208.79</v>
+        <v>58.99</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>3225.73</v>
+        <v>31.38</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>2354.09</v>
+        <v>15.47</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>3535.35</v>
+        <v>12.38</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>4176.56</v>
+        <v>3.7</v>
       </c>
       <c r="U84" s="34" t="n">
-        <v>13291.73</v>
+        <v>62.93</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>4577.35</v>
+        <v>34.55</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>4107.83</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>3738.06</v>
+        <v>3.4</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>1926.92</v>
+        <v>0</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>14350.16</v>
+        <v>103.46</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>1423.82</v>
+        <v>17.19</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>795.6799999999999</v>
+        <v>49.23</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17028,18 +16789,79 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>21.76</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="K85" s="9" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="U85" s="9" t="n"/>
-      <c r="Z85" s="9" t="n"/>
-      <c r="AB85" s="5" t="n"/>
+        <v>1478.05</v>
+      </c>
+      <c r="H85" s="18" t="n">
+        <v>3027</v>
+      </c>
+      <c r="I85" s="18" t="n">
+        <v>867.86</v>
+      </c>
+      <c r="J85" s="18" t="n">
+        <v>1824.02</v>
+      </c>
+      <c r="K85" s="34" t="n">
+        <v>7196.93</v>
+      </c>
+      <c r="L85" s="18" t="n">
+        <v>2952.28</v>
+      </c>
+      <c r="M85" s="18" t="n">
+        <v>5562.44</v>
+      </c>
+      <c r="N85" s="18" t="n">
+        <v>6195.16</v>
+      </c>
+      <c r="O85" s="18" t="n">
+        <v>5569.21</v>
+      </c>
+      <c r="P85" s="34" t="n">
+        <v>20279.09</v>
+      </c>
+      <c r="Q85" s="18" t="n">
+        <v>3225.73</v>
+      </c>
+      <c r="R85" s="18" t="n">
+        <v>2368.39</v>
+      </c>
+      <c r="S85" s="18" t="n">
+        <v>3537</v>
+      </c>
+      <c r="T85" s="18" t="n">
+        <v>4178.41</v>
+      </c>
+      <c r="U85" s="34" t="n">
+        <v>13309.53</v>
+      </c>
+      <c r="V85" s="18" t="n">
+        <v>4577.35</v>
+      </c>
+      <c r="W85" s="18" t="n">
+        <v>4107.83</v>
+      </c>
+      <c r="X85" s="18" t="n">
+        <v>3738.06</v>
+      </c>
+      <c r="Y85" s="18" t="n">
+        <v>2183.45</v>
+      </c>
+      <c r="Z85" s="34" t="n">
+        <v>14606.69</v>
+      </c>
+      <c r="AA85" s="18" t="n">
+        <v>1423.82</v>
+      </c>
+      <c r="AB85" s="19" t="n">
+        <v>799.4299999999999</v>
+      </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="11" t="n"/>
@@ -17060,68 +16882,47 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>36</v>
       </c>
       <c r="F86" s="9" t="n"/>
+      <c r="G86" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I86" s="18" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="K86" s="9" t="n"/>
       <c r="L86" s="18" t="n">
-        <v>247.41</v>
+        <v>18.9</v>
       </c>
       <c r="M86" s="18" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="N86" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="18" t="n">
-        <v>230.36</v>
-      </c>
       <c r="O86" s="18" t="n">
-        <v>419.19</v>
+        <v>0</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>896.96</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>2171.45</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>1030.02</v>
+        <v>70.3</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>390.64</v>
+        <v>1.65</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>578.59</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>4170.7</v>
-      </c>
-      <c r="V86" s="18" t="n">
-        <v>1143</v>
-      </c>
-      <c r="W86" s="18" t="n">
-        <v>1996.34</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>1572.58</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>1539.32</v>
-      </c>
-      <c r="Z86" s="34" t="n">
-        <v>6251.24</v>
-      </c>
-      <c r="AA86" s="18" t="n">
-        <v>8560.67</v>
-      </c>
-      <c r="AB86" s="19" t="n">
-        <v>13138.22</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="U86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
+      <c r="AB86" s="5" t="n"/>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -17142,27 +16943,79 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>-1351.47</v>
       </c>
       <c r="F87" s="9" t="n"/>
+      <c r="G87" s="18" t="n">
+        <v>-424.8</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>-1645.65</v>
+      </c>
       <c r="I87" s="18" t="n">
-        <v>500</v>
+        <v>28642.64</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>47.64</v>
-      </c>
-      <c r="K87" s="9" t="n"/>
+        <v>-3846.38</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>22725.81</v>
+      </c>
+      <c r="L87" s="18" t="n">
+        <v>-291</v>
+      </c>
+      <c r="M87" s="18" t="n">
+        <v>-4749.92</v>
+      </c>
       <c r="N87" s="18" t="n">
-        <v>0</v>
+        <v>-333.15</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="9" t="n"/>
-      <c r="U87" s="9" t="n"/>
-      <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="5" t="n"/>
+        <v>-2157.11</v>
+      </c>
+      <c r="P87" s="34" t="n">
+        <v>-7531.18</v>
+      </c>
+      <c r="Q87" s="18" t="n">
+        <v>-1353.79</v>
+      </c>
+      <c r="R87" s="18" t="n">
+        <v>-9374.719999999999</v>
+      </c>
+      <c r="S87" s="18" t="n">
+        <v>-416.38</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>-1384.92</v>
+      </c>
+      <c r="U87" s="34" t="n">
+        <v>-12529.81</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>-455.2</v>
+      </c>
+      <c r="W87" s="18" t="n">
+        <v>-6925.51</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>-7838.35</v>
+      </c>
+      <c r="Y87" s="18" t="n">
+        <v>-1504.48</v>
+      </c>
+      <c r="Z87" s="34" t="n">
+        <v>-16723.54</v>
+      </c>
+      <c r="AA87" s="18" t="n">
+        <v>-495.43</v>
+      </c>
+      <c r="AB87" s="19" t="n">
+        <v>-13109.61</v>
+      </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -17183,28 +17036,28 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="J88" s="18" t="n">
+      <c r="G88" s="18" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="N88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K88" s="9" t="n"/>
+      <c r="O88" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P88" s="9" t="n"/>
-      <c r="S88" s="18" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="U88" s="9" t="n"/>
-      <c r="X88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z88" s="9" t="n"/>
       <c r="AB88" s="5" t="n"/>
       <c r="AC88" s="10" t="n"/>
@@ -17227,51 +17080,42 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="9" t="n"/>
+      <c r="I89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K89" s="9" t="n"/>
+      <c r="N89" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="O89" s="18" t="n">
-        <v>1356.08</v>
+        <v>0</v>
       </c>
       <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="18" t="n">
-        <v>1441.54</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>975</v>
-      </c>
       <c r="S89" s="18" t="n">
-        <v>1706.58</v>
+        <v>0</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>933.8200000000001</v>
-      </c>
-      <c r="U89" s="34" t="n">
-        <v>5056.94</v>
-      </c>
-      <c r="V89" s="18" t="n">
-        <v>1328.75</v>
-      </c>
-      <c r="W89" s="18" t="n">
-        <v>776.8099999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U89" s="9" t="n"/>
       <c r="X89" s="18" t="n">
-        <v>1028.13</v>
+        <v>7372.16</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>717.54</v>
-      </c>
-      <c r="Z89" s="34" t="n">
-        <v>3851.23</v>
-      </c>
-      <c r="AA89" s="18" t="n">
-        <v>855.0599999999999</v>
-      </c>
-      <c r="AB89" s="19" t="n">
-        <v>773.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z89" s="9" t="n"/>
+      <c r="AB89" s="5" t="n"/>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -17292,33 +17136,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>-1636.57</v>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
-      <c r="P90" s="9" t="n"/>
-      <c r="U90" s="9" t="n"/>
+      <c r="G90" s="18" t="n">
+        <v>-16406.27</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>-2846.87</v>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>49325.89</v>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>-18521.09</v>
+      </c>
+      <c r="K90" s="34" t="n">
+        <v>11551.66</v>
+      </c>
+      <c r="L90" s="18" t="n">
+        <v>-20317.01</v>
+      </c>
+      <c r="M90" s="18" t="n">
+        <v>5055.22</v>
+      </c>
+      <c r="N90" s="18" t="n">
+        <v>-26298.31</v>
+      </c>
+      <c r="O90" s="18" t="n">
+        <v>8933.99</v>
+      </c>
+      <c r="P90" s="34" t="n">
+        <v>-32626.11</v>
+      </c>
+      <c r="Q90" s="18" t="n">
+        <v>42695.19</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>-47790.68</v>
+      </c>
+      <c r="S90" s="18" t="n">
+        <v>13696.15</v>
+      </c>
+      <c r="T90" s="18" t="n">
+        <v>-7411.07</v>
+      </c>
+      <c r="U90" s="34" t="n">
+        <v>1189.59</v>
+      </c>
       <c r="V90" s="18" t="n">
-        <v>455.2</v>
+        <v>2744.21</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>458.7</v>
+        <v>-5207.97</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>466.18</v>
+        <v>2378.55</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>464.65</v>
+        <v>3619.03</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>1844.73</v>
+        <v>3533.82</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>495.43</v>
+        <v>7392.62</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>537.2</v>
+        <v>7159</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -17333,6 +17222,501 @@
       <c r="AM90" s="10" t="n"/>
       <c r="AN90" s="10" t="n"/>
       <c r="AO90" s="11" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>-9182.83</v>
+      </c>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>33900.03</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>-1258.59</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>24831.14</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>-10244.28</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>47228.3</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>37151.72</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>2482.7</v>
+      </c>
+      <c r="N91" s="18" t="n">
+        <v>-13127.26</v>
+      </c>
+      <c r="O91" s="18" t="n">
+        <v>4365.47</v>
+      </c>
+      <c r="P91" s="34" t="n">
+        <v>30872.63</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>52296.02</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>-23874.41</v>
+      </c>
+      <c r="S91" s="18" t="n">
+        <v>11051.68</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>-7411.07</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>32062.22</v>
+      </c>
+      <c r="V91" s="18" t="n">
+        <v>34806.43</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>-5207.97</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>2378.55</v>
+      </c>
+      <c r="Y91" s="18" t="n">
+        <v>3619.03</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>35596.04</v>
+      </c>
+      <c r="AA91" s="18" t="n">
+        <v>42988.67</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>7158.99</v>
+      </c>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="11" t="n"/>
+      <c r="AK91" s="10" t="n"/>
+      <c r="AL91" s="10" t="n"/>
+      <c r="AM91" s="10" t="n"/>
+      <c r="AN91" s="10" t="n"/>
+      <c r="AO91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>1454.05</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>3027</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>827.36</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>1837.62</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>7146.03</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>2933.38</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>5511.04</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>6195.16</v>
+      </c>
+      <c r="O92" s="18" t="n">
+        <v>5569.21</v>
+      </c>
+      <c r="P92" s="34" t="n">
+        <v>20208.79</v>
+      </c>
+      <c r="Q92" s="18" t="n">
+        <v>3225.73</v>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>2354.09</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>3535.35</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>4176.56</v>
+      </c>
+      <c r="U92" s="34" t="n">
+        <v>13291.73</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>4577.35</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>4107.83</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>3738.06</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>1926.92</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>14350.16</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>1423.82</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>795.6799999999999</v>
+      </c>
+      <c r="AC92" s="10" t="n"/>
+      <c r="AD92" s="10" t="n"/>
+      <c r="AE92" s="11" t="n"/>
+      <c r="AF92" s="10" t="n"/>
+      <c r="AG92" s="10" t="n"/>
+      <c r="AH92" s="10" t="n"/>
+      <c r="AI92" s="10" t="n"/>
+      <c r="AJ92" s="11" t="n"/>
+      <c r="AK92" s="10" t="n"/>
+      <c r="AL92" s="10" t="n"/>
+      <c r="AM92" s="10" t="n"/>
+      <c r="AN92" s="10" t="n"/>
+      <c r="AO92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="18" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="K93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
+      <c r="U93" s="9" t="n"/>
+      <c r="Z93" s="9" t="n"/>
+      <c r="AB93" s="5" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="11" t="n"/>
+      <c r="AK93" s="10" t="n"/>
+      <c r="AL93" s="10" t="n"/>
+      <c r="AM93" s="10" t="n"/>
+      <c r="AN93" s="10" t="n"/>
+      <c r="AO93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="I94" s="18" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="9" t="n"/>
+      <c r="L94" s="18" t="n">
+        <v>247.41</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>419.19</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>896.96</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>2171.45</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>1030.02</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>390.64</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>578.59</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>4170.7</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>1143</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>1996.34</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>1572.58</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>1539.32</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>6251.24</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>8560.67</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>13138.22</v>
+      </c>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="11" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="10" t="n"/>
+      <c r="AM94" s="10" t="n"/>
+      <c r="AN94" s="10" t="n"/>
+      <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="I95" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="N95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="9" t="n"/>
+      <c r="U95" s="9" t="n"/>
+      <c r="Z95" s="9" t="n"/>
+      <c r="AB95" s="5" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="J96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="S96" s="18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U96" s="9" t="n"/>
+      <c r="X96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
+      <c r="AB96" s="5" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+      <c r="O97" s="18" t="n">
+        <v>1356.08</v>
+      </c>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="18" t="n">
+        <v>1441.54</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>1706.58</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>933.8200000000001</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>5056.94</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>1328.75</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>776.8099999999999</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>1028.13</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>717.54</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>3851.23</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>855.0599999999999</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>773.92</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
+      <c r="U98" s="9" t="n"/>
+      <c r="V98" s="18" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>466.18</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>464.65</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>1844.73</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>495.43</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>537.2</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17593,7 +17977,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5161,35 +5161,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5280,35 +5280,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5399,35 +5399,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5518,35 +5518,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5637,35 +5637,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5756,35 +5756,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5875,35 +5875,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5994,35 +5994,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6129,7 +6129,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>28100</v>
+        <v>26900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6311,7 +6311,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>27450</v>
+        <v>26750</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6402,7 +6402,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>28325</v>
+        <v>27850</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>28100</v>
+        <v>26900</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2125197627776282</v>
+        <v>0.2125197627776281</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.923996808725156</v>
+        <v>0.9239968087251555</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40147,7 +40147,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.7</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="32">
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5161,35 +5161,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5280,35 +5280,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5399,35 +5399,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5518,35 +5518,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5637,35 +5637,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5756,35 +5756,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5875,35 +5875,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5994,35 +5994,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6129,7 +6129,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>26900</v>
+        <v>26600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6311,7 +6311,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>26750</v>
+        <v>26450</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6402,7 +6402,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>27850</v>
+        <v>27587.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>26900</v>
+        <v>26600</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 28,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 27,950원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40147,7 +40147,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="32">
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -5161,35 +5161,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5280,35 +5280,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5399,35 +5399,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5518,35 +5518,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5637,35 +5637,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5756,35 +5756,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5875,35 +5875,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5994,35 +5994,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6129,7 +6129,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>26600</v>
+        <v>26250</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6311,7 +6311,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>26450</v>
+        <v>26150</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6402,7 +6402,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>27587.5</v>
+        <v>27330</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>26600</v>
+        <v>26250</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 27,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,750원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40147,7 +40147,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.7</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="32">
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -958,61 +958,61 @@
     <comment ref="AC26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AD26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AF26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AG26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AH26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AI26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AK26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AL26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AM26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AN26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)</t>
+최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)</t>
       </text>
     </comment>
     <comment ref="AC27" authorId="0" shapeId="0">
@@ -1555,79 +1555,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 535원 유지</t>
       </text>
     </comment>
-    <comment ref="AI41" authorId="0" shapeId="0">
+    <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 535원 유지</t>
       </text>
     </comment>
-    <comment ref="AN41" authorId="0" shapeId="0">
+    <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 535원 유지</t>
@@ -2005,121 +1945,121 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1085억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1156억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1188억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1258억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1290억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1361억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1395억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1465억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1365억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1435억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1482억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1551억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1598억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1667억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1717억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1786억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1701억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1769억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1826억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1894억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1085억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1156억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1188억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1258억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1290억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1361억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1395억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1465억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1365억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1435억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1482억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1551억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1598억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1667억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1717억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1786억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1701억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1769억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1826억 × 3.01%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1894억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2355,61 +2295,61 @@
     </comment>
     <comment ref="AC15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN15" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +8.17억의 50% 초과 → 0(경고)
+        <t>추정: 최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)
 [abs]</t>
       </text>
     </comment>
@@ -3288,159 +3228,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Y33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AA33" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="AB33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 589억 − (비영업손익 794억 − 12분기 기준선 55억) × (1 − 20.4%, 분기 유효세율(법인세 177억 ÷ 세전 866억)) × 지배 비중 0.85(그 분기 지배NI/NI) = 86억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 2,293.6원</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 739억 × (1 − 세율 20.4% [분기 유효세율(법인세 177억 ÷ 세전 866억)]) × 지배 비중 0.8544 [그 분기 지배NI/NI] = 86억 ÷ 유통주식수 · 초과 = 비영업손익 794억 − 12분기 기준선 55억 · 보고 EPS 2,294원(EPS 행 불변) · 상수 588.5·0.8544 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN33" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
@@ -4274,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4290,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4178,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4289,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.01% / 부채 0.00% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0301, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": null}</t>
+          <t>· 이자율 자산 2.77% / 부채 0.00% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0277, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": null}</t>
         </is>
       </c>
     </row>
@@ -4453,50 +4303,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 2,294→조정 336원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 8.5/9.1/12.0배(hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/023160.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/023160.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 794억(영업이익 72억의 11배, 12분기 중위 55억·기준선 55억) → 지배NI 589억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 335.9원(보고 2,293.6원; 초과 비영업손익 739억 × (1 − 세율 20.4%) × 지배 비중 0.85 = 503억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +20.6억이 이자손익 추정 +8.2억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +278/+141/+280/+791(중위 +279억) → 추정 2026Q3 +8억(차 -271억, -97%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 794억(영업이익 72억의 11배, 12분기 중위 55억·기준선 55억) → 지배NI 589억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 335.9원(보고 2,293.6원; 초과 비영업손익 739억 × (1 − 세율 20.4%) × 지배 비중 0.85 = 503억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +20.6억이 이자손익 추정 +8.0억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +278/+141/+280/+791(중위 +279억) → 추정 2026Q3 +8억(차 -271억, -97%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 26.1, "op_wape_pct": 27.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 569.88, "rev_act": 814.15, "op_pred": 76.42, "op_act": 115.69}, {"q": "2025Q4", "rev_pred": 610.49, "rev_act": 806.0, "op_pred": 81.87, "op_act": 121.05}, {"q": "2026Q1", "rev_pred": 578.02, "rev_act": 822.75, "op_pred": 77.51, "op_act": 93.5}, {"q": "2026Q2", "rev_pred": 667.36, "rev_act": 837.46, "op_pred": 89.49, "op_act": 72.12}]}</t>
         </is>
@@ -4513,7 +4370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO59"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6700,11 +6557,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6712,19 +6569,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6732,19 +6589,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -7640,11 +7497,11 @@
         <v/>
       </c>
       <c r="AC28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AD28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AE28" s="25">
@@ -7652,19 +7509,19 @@
         <v/>
       </c>
       <c r="AF28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AG28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AH28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AI28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AJ28" s="25">
@@ -7672,19 +7529,19 @@
         <v/>
       </c>
       <c r="AK28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AL28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AM28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AN28" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AO28" s="25">
@@ -7805,11 +7662,11 @@
         <v/>
       </c>
       <c r="AC29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AD29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AE29" s="25">
@@ -7817,19 +7674,19 @@
         <v/>
       </c>
       <c r="AF29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AG29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AH29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AI29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AJ29" s="25">
@@ -7837,19 +7694,19 @@
         <v/>
       </c>
       <c r="AK29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AL29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AM29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AN29" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AO29" s="25">
@@ -8080,36 +7937,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>1.566e-05</v>
+        <v>0.001426637</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002676685</v>
+        <v>-0.006432463</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.004810845</v>
+        <v>0.005158254</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>137.408187178</v>
+        <v>137.416409925</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.000212224</v>
+        <v>0.001358742</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.003969026</v>
+        <v>-0.002688399</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.000764269</v>
+        <v>-0.003877286</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>137.409199488</v>
+        <v>137.41489207</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.002099733</v>
+        <v>-0.001249449</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.002501488</v>
+        <v>0.000347983</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8208,36 +8065,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.002147237</v>
+        <v>-0.002710044</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.005186271</v>
+        <v>-0.002047167</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.010309962</v>
+        <v>0.006312485</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>137.414062151</v>
+        <v>137.411845221</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.001144535</v>
+        <v>0.000648768</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.005017083</v>
+        <v>0.001121743</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.00012658</v>
+        <v>-0.007415714</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>137.406512239</v>
+        <v>137.413775424</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.007020497</v>
+        <v>-0.001036902</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.003193351</v>
+        <v>-0.003067668</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8552,36 +8409,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.0947771</v>
+        <v>0.08884642399999999</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.08627338700000001</v>
+        <v>0.081284272</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.081429059</v>
+        <v>0.077033324</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>-0.021496205</v>
+        <v>-0.020670265</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.085280631</v>
+        <v>0.080935126</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.078322849</v>
+        <v>0.07458501200000001</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.074455433</v>
+        <v>0.071123909</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.009204509</v>
+        <v>-0.009106642</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.073579303</v>
+        <v>0.07047618999999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.068306415</v>
+        <v>0.06558285899999999</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9042,264 +8899,176 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21">
-        <f>IFERROR(subQ!J33/subQ!E33-1,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="22" t="n"/>
-      <c r="L40" s="21">
-        <f>IFERROR(subQ!L33/subQ!G33-1,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="21">
-        <f>IFERROR(subQ!M33/subQ!H33-1,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="21">
-        <f>IFERROR(subQ!N33/subQ!I33-1,"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="21">
-        <f>IFERROR(subQ!O33/subQ!J33-1,"")</f>
-        <v/>
-      </c>
-      <c r="P40" s="22" t="n"/>
-      <c r="Q40" s="21">
-        <f>IFERROR(subQ!Q33/subQ!L33-1,"")</f>
-        <v/>
-      </c>
-      <c r="R40" s="21">
-        <f>IFERROR(subQ!R33/subQ!M33-1,"")</f>
-        <v/>
-      </c>
-      <c r="S40" s="21">
-        <f>IFERROR(subQ!S33/subQ!N33-1,"")</f>
-        <v/>
-      </c>
-      <c r="T40" s="21">
-        <f>IFERROR(subQ!T33/subQ!O33-1,"")</f>
-        <v/>
-      </c>
-      <c r="U40" s="22" t="n"/>
-      <c r="V40" s="21">
-        <f>IFERROR(subQ!V33/subQ!Q33-1,"")</f>
-        <v/>
-      </c>
-      <c r="W40" s="21">
-        <f>IFERROR(subQ!W33/subQ!R33-1,"")</f>
-        <v/>
-      </c>
-      <c r="X40" s="21">
-        <f>IFERROR(subQ!X33/subQ!S33-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y40" s="21">
-        <f>IFERROR(subQ!Y33/subQ!T33-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z40" s="22" t="n"/>
-      <c r="AA40" s="21">
-        <f>IFERROR(subQ!AA33/subQ!V33-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB40" s="23">
-        <f>IFERROR(subQ!AB33/subQ!W33-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC40" s="24" t="n">
-        <v>-0.669643655</v>
-      </c>
-      <c r="AD40" s="24" t="n">
-        <v>-0.04803719</v>
-      </c>
-      <c r="AE40" s="25" t="n"/>
-      <c r="AF40" s="24" t="n">
-        <v>-0.63781867</v>
-      </c>
-      <c r="AG40" s="24" t="n">
-        <v>0.150342364</v>
-      </c>
-      <c r="AH40" s="24" t="n">
-        <v>0.132197891</v>
-      </c>
-      <c r="AI40" s="24" t="n">
-        <v>0.132392838</v>
-      </c>
-      <c r="AJ40" s="25" t="n"/>
-      <c r="AK40" s="24" t="n">
-        <v>0.132310135</v>
-      </c>
-      <c r="AL40" s="24" t="n">
-        <v>0.132246377</v>
-      </c>
-      <c r="AM40" s="24" t="n">
-        <v>0.07497612200000001</v>
-      </c>
-      <c r="AN40" s="24" t="n">
-        <v>0.074988021</v>
-      </c>
-      <c r="AO40" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E40" s="27">
+        <f>subQ!E35</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>subQ!F35</f>
+        <v/>
+      </c>
+      <c r="G40" s="27">
+        <f>subQ!G35</f>
+        <v/>
+      </c>
+      <c r="H40" s="27">
+        <f>subQ!H35</f>
+        <v/>
+      </c>
+      <c r="I40" s="27">
+        <f>subQ!I35</f>
+        <v/>
+      </c>
+      <c r="J40" s="27">
+        <f>subQ!J35</f>
+        <v/>
+      </c>
+      <c r="K40" s="28">
+        <f>subQ!K35</f>
+        <v/>
+      </c>
+      <c r="L40" s="27">
+        <f>subQ!L35</f>
+        <v/>
+      </c>
+      <c r="M40" s="27">
+        <f>subQ!M35</f>
+        <v/>
+      </c>
+      <c r="N40" s="27">
+        <f>subQ!N35</f>
+        <v/>
+      </c>
+      <c r="O40" s="27">
+        <f>subQ!O35</f>
+        <v/>
+      </c>
+      <c r="P40" s="28">
+        <f>subQ!P35</f>
+        <v/>
+      </c>
+      <c r="Q40" s="27">
+        <f>subQ!Q35</f>
+        <v/>
+      </c>
+      <c r="R40" s="27">
+        <f>subQ!R35</f>
+        <v/>
+      </c>
+      <c r="S40" s="27">
+        <f>subQ!S35</f>
+        <v/>
+      </c>
+      <c r="T40" s="27">
+        <f>subQ!T35</f>
+        <v/>
+      </c>
+      <c r="U40" s="28">
+        <f>subQ!U35</f>
+        <v/>
+      </c>
+      <c r="V40" s="27">
+        <f>subQ!V35</f>
+        <v/>
+      </c>
+      <c r="W40" s="27">
+        <f>subQ!W35</f>
+        <v/>
+      </c>
+      <c r="X40" s="27">
+        <f>subQ!X35</f>
+        <v/>
+      </c>
+      <c r="Y40" s="27">
+        <f>subQ!Y35</f>
+        <v/>
+      </c>
+      <c r="Z40" s="28">
+        <f>subQ!Z35</f>
+        <v/>
+      </c>
+      <c r="AA40" s="27">
+        <f>subQ!AA35</f>
+        <v/>
+      </c>
+      <c r="AB40" s="29">
+        <f>subQ!AB35</f>
+        <v/>
+      </c>
+      <c r="AC40" s="33" t="n"/>
+      <c r="AD40" s="30" t="n">
+        <v>535</v>
+      </c>
+      <c r="AE40" s="31">
+        <f>subQ!AE35</f>
+        <v/>
+      </c>
+      <c r="AF40" s="33" t="n"/>
+      <c r="AG40" s="33" t="n"/>
+      <c r="AH40" s="33" t="n"/>
+      <c r="AI40" s="30" t="n">
+        <v>535</v>
+      </c>
+      <c r="AJ40" s="31">
+        <f>subQ!AJ35</f>
+        <v/>
+      </c>
+      <c r="AK40" s="33" t="n"/>
+      <c r="AL40" s="33" t="n"/>
+      <c r="AM40" s="33" t="n"/>
+      <c r="AN40" s="30" t="n">
+        <v>535</v>
+      </c>
+      <c r="AO40" s="31">
+        <f>subQ!AO35</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E41" s="27">
-        <f>subQ!E35</f>
-        <v/>
-      </c>
-      <c r="F41" s="28">
-        <f>subQ!F35</f>
-        <v/>
-      </c>
-      <c r="G41" s="27">
-        <f>subQ!G35</f>
-        <v/>
-      </c>
-      <c r="H41" s="27">
-        <f>subQ!H35</f>
-        <v/>
-      </c>
-      <c r="I41" s="27">
-        <f>subQ!I35</f>
-        <v/>
-      </c>
-      <c r="J41" s="27">
-        <f>subQ!J35</f>
-        <v/>
-      </c>
-      <c r="K41" s="28">
-        <f>subQ!K35</f>
-        <v/>
-      </c>
-      <c r="L41" s="27">
-        <f>subQ!L35</f>
-        <v/>
-      </c>
-      <c r="M41" s="27">
-        <f>subQ!M35</f>
-        <v/>
-      </c>
-      <c r="N41" s="27">
-        <f>subQ!N35</f>
-        <v/>
-      </c>
-      <c r="O41" s="27">
-        <f>subQ!O35</f>
-        <v/>
-      </c>
-      <c r="P41" s="28">
-        <f>subQ!P35</f>
-        <v/>
-      </c>
-      <c r="Q41" s="27">
-        <f>subQ!Q35</f>
-        <v/>
-      </c>
-      <c r="R41" s="27">
-        <f>subQ!R35</f>
-        <v/>
-      </c>
-      <c r="S41" s="27">
-        <f>subQ!S35</f>
-        <v/>
-      </c>
-      <c r="T41" s="27">
-        <f>subQ!T35</f>
-        <v/>
-      </c>
-      <c r="U41" s="28">
-        <f>subQ!U35</f>
-        <v/>
-      </c>
-      <c r="V41" s="27">
-        <f>subQ!V35</f>
-        <v/>
-      </c>
-      <c r="W41" s="27">
-        <f>subQ!W35</f>
-        <v/>
-      </c>
-      <c r="X41" s="27">
-        <f>subQ!X35</f>
-        <v/>
-      </c>
-      <c r="Y41" s="27">
-        <f>subQ!Y35</f>
-        <v/>
-      </c>
-      <c r="Z41" s="28">
-        <f>subQ!Z35</f>
-        <v/>
-      </c>
-      <c r="AA41" s="27">
-        <f>subQ!AA35</f>
-        <v/>
-      </c>
-      <c r="AB41" s="29">
-        <f>subQ!AB35</f>
-        <v/>
-      </c>
-      <c r="AC41" s="33" t="n"/>
-      <c r="AD41" s="30" t="n">
-        <v>535</v>
-      </c>
-      <c r="AE41" s="31">
-        <f>subQ!AE35</f>
-        <v/>
-      </c>
-      <c r="AF41" s="33" t="n"/>
-      <c r="AG41" s="33" t="n"/>
-      <c r="AH41" s="33" t="n"/>
-      <c r="AI41" s="30" t="n">
-        <v>535</v>
-      </c>
-      <c r="AJ41" s="31">
-        <f>subQ!AJ35</f>
-        <v/>
-      </c>
-      <c r="AK41" s="33" t="n"/>
-      <c r="AL41" s="33" t="n"/>
-      <c r="AM41" s="33" t="n"/>
-      <c r="AN41" s="30" t="n">
-        <v>535</v>
-      </c>
-      <c r="AO41" s="31">
-        <f>subQ!AO35</f>
-        <v/>
-      </c>
+      <c r="F41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AB41" s="5" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="11" t="n"/>
+      <c r="AK41" s="10" t="n"/>
+      <c r="AL41" s="10" t="n"/>
+      <c r="AM41" s="10" t="n"/>
+      <c r="AN41" s="10" t="n"/>
+      <c r="AO41" s="11" t="n"/>
     </row>
     <row r="42">
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
@@ -9321,14 +9090,22 @@
       <c r="AO42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>26250</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,750원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9354,20 +9131,22 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D44" s="34" t="n">
-        <v>26250</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,750원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9393,22 +9172,20 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D45" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9434,20 +9211,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>8.5</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9473,20 +9250,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D47" s="30" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9512,20 +9289,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9551,20 +9328,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>12</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9590,20 +9367,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="n">
+        <v>0.2125156653534312</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2125) · 최근 12분기 유효세율 21.3%(5~27% 안 — 그대로)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9629,20 +9406,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2125197627776281</v>
+        <v>0.1843357257761786</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2125) · 최근 12분기 유효세율 21.3%(5~27% 안 — 그대로)</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1843)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9668,20 +9445,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1843357257761786</v>
+        <v>0.9239723919637756</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1843)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9707,20 +9484,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.9239968087251555</v>
+        <v>0.02766838073366952</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0277)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -9746,20 +9523,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03012613884061626</v>
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0301)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -9785,20 +9562,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>0</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="n">
+        <v>0.2151</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -9824,20 +9601,18 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="n">
-        <v>0.2151</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -9863,18 +9638,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -9900,15 +9675,15 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -9933,43 +9708,6 @@
       <c r="AM58" s="10" t="n"/>
       <c r="AN58" s="10" t="n"/>
       <c r="AO58" s="11" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="U59" s="9" t="n"/>
-      <c r="Z59" s="9" t="n"/>
-      <c r="AB59" s="5" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="11" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="11" t="n"/>
-      <c r="AK59" s="10" t="n"/>
-      <c r="AL59" s="10" t="n"/>
-      <c r="AM59" s="10" t="n"/>
-      <c r="AN59" s="10" t="n"/>
-      <c r="AO59" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10231,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11024,9 +10762,33 @@
       <c r="S10" s="18" t="n">
         <v>46312.56</v>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="Z10" s="9" t="n"/>
-      <c r="AB10" s="5" t="n"/>
+      <c r="T10" s="18" t="n">
+        <v>33518.65</v>
+      </c>
+      <c r="U10" s="37" t="n">
+        <v>33518.65</v>
+      </c>
+      <c r="V10" s="18" t="n">
+        <v>34723.19</v>
+      </c>
+      <c r="W10" s="18" t="n">
+        <v>31218</v>
+      </c>
+      <c r="X10" s="18" t="n">
+        <v>21483.62</v>
+      </c>
+      <c r="Y10" s="18" t="n">
+        <v>20314.31</v>
+      </c>
+      <c r="Z10" s="37" t="n">
+        <v>20314.31</v>
+      </c>
+      <c r="AA10" s="18" t="n">
+        <v>10429.69</v>
+      </c>
+      <c r="AB10" s="19" t="n">
+        <v>14781.62</v>
+      </c>
       <c r="AC10" s="10" t="n"/>
       <c r="AD10" s="10" t="n"/>
       <c r="AE10" s="11" t="n"/>
@@ -11476,31 +11238,31 @@
         <v>88736.92999999999</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>79400.64999999999</v>
+        <v>85142.67999999999</v>
       </c>
       <c r="U15" s="37" t="n">
-        <v>79400.64999999999</v>
+        <v>85142.67999999999</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>83340.94</v>
+        <v>90382.97</v>
       </c>
       <c r="W15" s="18" t="n">
-        <v>80802.69</v>
+        <v>87844.72</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>60402.02</v>
+        <v>69426.81</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>52355.11</v>
+        <v>61379.9</v>
       </c>
       <c r="Z15" s="37" t="n">
-        <v>52355.11</v>
+        <v>61379.9</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>53388.48</v>
+        <v>62413.27</v>
       </c>
       <c r="AB15" s="19" t="n">
-        <v>58332.87</v>
+        <v>65415.01</v>
       </c>
       <c r="AC15" s="10" t="n"/>
       <c r="AD15" s="10" t="n"/>
@@ -11571,31 +11333,31 @@
         <v>88736.92999999999</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>79400.64999999999</v>
+        <v>85142.67999999999</v>
       </c>
       <c r="U16" s="37" t="n">
-        <v>79400.64999999999</v>
+        <v>85142.67999999999</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>83340.94</v>
+        <v>90382.97</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>80802.69</v>
+        <v>87844.72</v>
       </c>
       <c r="X16" s="18" t="n">
-        <v>60402.02</v>
+        <v>69426.81</v>
       </c>
       <c r="Y16" s="18" t="n">
-        <v>52355.11</v>
+        <v>61379.9</v>
       </c>
       <c r="Z16" s="37" t="n">
-        <v>52355.11</v>
+        <v>61379.9</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>53388.48</v>
+        <v>62413.27</v>
       </c>
       <c r="AB16" s="19" t="n">
-        <v>58332.87</v>
+        <v>65415.01</v>
       </c>
       <c r="AC16" s="10" t="n"/>
       <c r="AD16" s="10" t="n"/>
@@ -14504,31 +14266,31 @@
         <v>156522.19</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>111462.87</v>
+        <v>117204.9</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>111462.87</v>
+        <v>117204.9</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>118147.37</v>
+        <v>125189.4</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>110401.15</v>
+        <v>117443.18</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>92379.03</v>
+        <v>101403.82</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>87951.14999999999</v>
+        <v>96975.94</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>87951.14999999999</v>
+        <v>96975.94</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>96377.14999999999</v>
+        <v>105401.94</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>108480.53</v>
+        <v>115562.67</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -19007,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19800,9 +19562,33 @@
       <c r="S10" s="18" t="n">
         <v>37568.32</v>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="Z10" s="9" t="n"/>
-      <c r="AB10" s="5" t="n"/>
+      <c r="T10" s="18" t="n">
+        <v>16933.52</v>
+      </c>
+      <c r="U10" s="37" t="n">
+        <v>16933.52</v>
+      </c>
+      <c r="V10" s="18" t="n">
+        <v>18494.5</v>
+      </c>
+      <c r="W10" s="18" t="n">
+        <v>18120.16</v>
+      </c>
+      <c r="X10" s="18" t="n">
+        <v>18275.88</v>
+      </c>
+      <c r="Y10" s="18" t="n">
+        <v>17008.4</v>
+      </c>
+      <c r="Z10" s="37" t="n">
+        <v>17008.4</v>
+      </c>
+      <c r="AA10" s="18" t="n">
+        <v>9008.4</v>
+      </c>
+      <c r="AB10" s="19" t="n">
+        <v>9008.4</v>
+      </c>
       <c r="AC10" s="10" t="n"/>
       <c r="AD10" s="10" t="n"/>
       <c r="AE10" s="11" t="n"/>
@@ -27822,11 +27608,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB27*변수!$D$54-AB25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AB27*변수!$D$53-AB25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC27*변수!$D$54-AC25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AC27*변수!$D$53-AC25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -27834,19 +27620,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD27*변수!$D$54-AD25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AD27*변수!$D$53-AD25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF27*변수!$D$54-AF25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AF27*변수!$D$53-AF25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG27*변수!$D$54-AG25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AG27*변수!$D$53-AG25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH27*변수!$D$54-AH25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AH27*변수!$D$53-AH25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -27854,19 +27640,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI27*변수!$D$54-AI25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AI27*변수!$D$53-AI25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK27*변수!$D$54-AK25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AK27*변수!$D$53-AK25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL27*변수!$D$54-AL25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AL27*변수!$D$53-AL25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM27*변수!$D$54-AM25*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AM27*변수!$D$53-AM25*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -30934,86 +30720,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E33" s="18" t="n">
-        <v>112.7</v>
+      <c r="E33" s="18">
+        <f>IFERROR(E32,"")</f>
+        <v/>
       </c>
       <c r="F33" s="37" t="n"/>
-      <c r="G33" s="18" t="n">
-        <v>297.2</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>467.2</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>336.1</v>
-      </c>
-      <c r="J33" s="18" t="n">
-        <v>282.4</v>
+      <c r="G33" s="18">
+        <f>IFERROR(G32,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>IFERROR(H32,"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="18">
+        <f>IFERROR(I32,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="18">
+        <f>IFERROR(J32,"")</f>
+        <v/>
       </c>
       <c r="K33" s="37">
         <f>SUM(G33:J33)</f>
         <v/>
       </c>
-      <c r="L33" s="18" t="n">
-        <v>749.5</v>
-      </c>
-      <c r="M33" s="18" t="n">
-        <v>658.6</v>
-      </c>
-      <c r="N33" s="18" t="n">
-        <v>444.2</v>
-      </c>
-      <c r="O33" s="18" t="n">
-        <v>276.9</v>
+      <c r="L33" s="18">
+        <f>IFERROR(L32,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="18">
+        <f>IFERROR(M32,"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="18">
+        <f>IFERROR(N32,"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="18">
+        <f>IFERROR(O32,"")</f>
+        <v/>
       </c>
       <c r="P33" s="37">
         <f>SUM(L33:O33)</f>
         <v/>
       </c>
-      <c r="Q33" s="18" t="n">
-        <v>626</v>
-      </c>
-      <c r="R33" s="18" t="n">
-        <v>389.1</v>
-      </c>
-      <c r="S33" s="18" t="n">
-        <v>268.3</v>
-      </c>
-      <c r="T33" s="18" t="n">
-        <v>452.9</v>
+      <c r="Q33" s="18">
+        <f>IFERROR(Q32,"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="18">
+        <f>IFERROR(R32,"")</f>
+        <v/>
+      </c>
+      <c r="S33" s="18">
+        <f>IFERROR(S32,"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="18">
+        <f>IFERROR(T32,"")</f>
+        <v/>
       </c>
       <c r="U33" s="37">
         <f>SUM(Q33:T33)</f>
         <v/>
       </c>
-      <c r="V33" s="18" t="n">
-        <v>394.9</v>
-      </c>
-      <c r="W33" s="18" t="n">
-        <v>567.4</v>
-      </c>
-      <c r="X33" s="18" t="n">
-        <v>1119.7</v>
-      </c>
-      <c r="Y33" s="18" t="n">
-        <v>387.2</v>
+      <c r="V33" s="18">
+        <f>IFERROR(V32,"")</f>
+        <v/>
+      </c>
+      <c r="W33" s="18">
+        <f>IFERROR(W32,"")</f>
+        <v/>
+      </c>
+      <c r="X33" s="18">
+        <f>IFERROR(X32,"")</f>
+        <v/>
+      </c>
+      <c r="Y33" s="18">
+        <f>IFERROR(Y32,"")</f>
+        <v/>
       </c>
       <c r="Z33" s="37">
         <f>SUM(V33:Y33)</f>
         <v/>
       </c>
-      <c r="AA33" s="18" t="n">
-        <v>1043.4</v>
-      </c>
-      <c r="AB33" s="39" t="n">
-        <v>335.9</v>
+      <c r="AA33" s="18">
+        <f>IFERROR(AA32,"")</f>
+        <v/>
+      </c>
+      <c r="AB33" s="39">
+        <f>IFERROR((AB20-(588.5)*(0.8544))*100/AB31,"")</f>
+        <v/>
       </c>
       <c r="AC33" s="20">
-        <f>IFERROR(X33*(1+변수!AC40),"")</f>
+        <f>IFERROR(AC32,"")</f>
         <v/>
       </c>
       <c r="AD33" s="20">
-        <f>IFERROR(Y33*(1+변수!AD40),"")</f>
+        <f>IFERROR(AD32,"")</f>
         <v/>
       </c>
       <c r="AE33" s="38">
@@ -31021,19 +30826,19 @@
         <v/>
       </c>
       <c r="AF33" s="20">
-        <f>IFERROR(AA33*(1+변수!AF40),"")</f>
+        <f>IFERROR(AF32,"")</f>
         <v/>
       </c>
       <c r="AG33" s="20">
-        <f>IFERROR(AB33*(1+변수!AG40),"")</f>
+        <f>IFERROR(AG32,"")</f>
         <v/>
       </c>
       <c r="AH33" s="20">
-        <f>IFERROR(AC33*(1+변수!AH40),"")</f>
+        <f>IFERROR(AH32,"")</f>
         <v/>
       </c>
       <c r="AI33" s="20">
-        <f>IFERROR(AD33*(1+변수!AI40),"")</f>
+        <f>IFERROR(AI32,"")</f>
         <v/>
       </c>
       <c r="AJ33" s="38">
@@ -31041,19 +30846,19 @@
         <v/>
       </c>
       <c r="AK33" s="20">
-        <f>IFERROR(AF33*(1+변수!AK40),"")</f>
+        <f>IFERROR(AK32,"")</f>
         <v/>
       </c>
       <c r="AL33" s="20">
-        <f>IFERROR(AG33*(1+변수!AL40),"")</f>
+        <f>IFERROR(AL32,"")</f>
         <v/>
       </c>
       <c r="AM33" s="20">
-        <f>IFERROR(AH33*(1+변수!AM40),"")</f>
+        <f>IFERROR(AM32,"")</f>
         <v/>
       </c>
       <c r="AN33" s="20">
-        <f>IFERROR(AI33*(1+변수!AN40),"")</f>
+        <f>IFERROR(AN32,"")</f>
         <v/>
       </c>
       <c r="AO33" s="38">
@@ -31302,7 +31107,7 @@
       <c r="AB35" s="19" t="n"/>
       <c r="AC35" s="20" t="n"/>
       <c r="AD35" s="20">
-        <f>변수!AD41</f>
+        <f>변수!AD40</f>
         <v/>
       </c>
       <c r="AE35" s="38">
@@ -31313,7 +31118,7 @@
       <c r="AG35" s="20" t="n"/>
       <c r="AH35" s="20" t="n"/>
       <c r="AI35" s="20">
-        <f>변수!AI41</f>
+        <f>변수!AI40</f>
         <v/>
       </c>
       <c r="AJ35" s="38">
@@ -31324,7 +31129,7 @@
       <c r="AL35" s="20" t="n"/>
       <c r="AM35" s="20" t="n"/>
       <c r="AN35" s="20">
-        <f>변수!AN41</f>
+        <f>변수!AN40</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -31441,11 +31246,11 @@
         <v/>
       </c>
       <c r="AC36" s="40">
-        <f>IFERROR(변수!$D$44/(Y32+AA32+AB32+AC32),"")</f>
+        <f>IFERROR(변수!$D$43/(Y32+AA32+AB32+AC32),"")</f>
         <v/>
       </c>
       <c r="AD36" s="40">
-        <f>IFERROR(변수!$D$44/(AA32+AB32+AC32+AD32),"")</f>
+        <f>IFERROR(변수!$D$43/(AA32+AB32+AC32+AD32),"")</f>
         <v/>
       </c>
       <c r="AE36" s="41">
@@ -31453,19 +31258,19 @@
         <v/>
       </c>
       <c r="AF36" s="40">
-        <f>IFERROR(변수!$D$44/(AB32+AC32+AD32+AF32),"")</f>
+        <f>IFERROR(변수!$D$43/(AB32+AC32+AD32+AF32),"")</f>
         <v/>
       </c>
       <c r="AG36" s="40">
-        <f>IFERROR(변수!$D$44/(AC32+AD32+AF32+AG32),"")</f>
+        <f>IFERROR(변수!$D$43/(AC32+AD32+AF32+AG32),"")</f>
         <v/>
       </c>
       <c r="AH36" s="40">
-        <f>IFERROR(변수!$D$44/(AD32+AF32+AG32+AH32),"")</f>
+        <f>IFERROR(변수!$D$43/(AD32+AF32+AG32+AH32),"")</f>
         <v/>
       </c>
       <c r="AI36" s="40">
-        <f>IFERROR(변수!$D$44/(AF32+AG32+AH32+AI32),"")</f>
+        <f>IFERROR(변수!$D$43/(AF32+AG32+AH32+AI32),"")</f>
         <v/>
       </c>
       <c r="AJ36" s="41">
@@ -31473,19 +31278,19 @@
         <v/>
       </c>
       <c r="AK36" s="40">
-        <f>IFERROR(변수!$D$44/(AG32+AH32+AI32+AK32),"")</f>
+        <f>IFERROR(변수!$D$43/(AG32+AH32+AI32+AK32),"")</f>
         <v/>
       </c>
       <c r="AL36" s="40">
-        <f>IFERROR(변수!$D$44/(AH32+AI32+AK32+AL32),"")</f>
+        <f>IFERROR(변수!$D$43/(AH32+AI32+AK32+AL32),"")</f>
         <v/>
       </c>
       <c r="AM36" s="40">
-        <f>IFERROR(변수!$D$44/(AI32+AK32+AL32+AM32),"")</f>
+        <f>IFERROR(변수!$D$43/(AI32+AK32+AL32+AM32),"")</f>
         <v/>
       </c>
       <c r="AN36" s="40">
-        <f>IFERROR(변수!$D$44/(AK32+AL32+AM32+AN32),"")</f>
+        <f>IFERROR(변수!$D$43/(AK32+AL32+AM32+AN32),"")</f>
         <v/>
       </c>
       <c r="AO36" s="41">
@@ -31611,11 +31416,11 @@
         <v/>
       </c>
       <c r="AC37" s="40">
-        <f>IFERROR(변수!$D$44/AC34,"")</f>
+        <f>IFERROR(변수!$D$43/AC34,"")</f>
         <v/>
       </c>
       <c r="AD37" s="40">
-        <f>IFERROR(변수!$D$44/AD34,"")</f>
+        <f>IFERROR(변수!$D$43/AD34,"")</f>
         <v/>
       </c>
       <c r="AE37" s="41">
@@ -31623,19 +31428,19 @@
         <v/>
       </c>
       <c r="AF37" s="40">
-        <f>IFERROR(변수!$D$44/AF34,"")</f>
+        <f>IFERROR(변수!$D$43/AF34,"")</f>
         <v/>
       </c>
       <c r="AG37" s="40">
-        <f>IFERROR(변수!$D$44/AG34,"")</f>
+        <f>IFERROR(변수!$D$43/AG34,"")</f>
         <v/>
       </c>
       <c r="AH37" s="40">
-        <f>IFERROR(변수!$D$44/AH34,"")</f>
+        <f>IFERROR(변수!$D$43/AH34,"")</f>
         <v/>
       </c>
       <c r="AI37" s="40">
-        <f>IFERROR(변수!$D$44/AI34,"")</f>
+        <f>IFERROR(변수!$D$43/AI34,"")</f>
         <v/>
       </c>
       <c r="AJ37" s="41">
@@ -31643,19 +31448,19 @@
         <v/>
       </c>
       <c r="AK37" s="40">
-        <f>IFERROR(변수!$D$44/AK34,"")</f>
+        <f>IFERROR(변수!$D$43/AK34,"")</f>
         <v/>
       </c>
       <c r="AL37" s="40">
-        <f>IFERROR(변수!$D$44/AL34,"")</f>
+        <f>IFERROR(변수!$D$43/AL34,"")</f>
         <v/>
       </c>
       <c r="AM37" s="40">
-        <f>IFERROR(변수!$D$44/AM34,"")</f>
+        <f>IFERROR(변수!$D$43/AM34,"")</f>
         <v/>
       </c>
       <c r="AN37" s="40">
-        <f>IFERROR(변수!$D$44/AN34,"")</f>
+        <f>IFERROR(변수!$D$43/AN34,"")</f>
         <v/>
       </c>
       <c r="AO37" s="41">
@@ -32689,7 +32494,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
       <c r="W2" s="43" t="n"/>
@@ -37950,7 +37755,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
       <c r="I2" s="43" t="n"/>
@@ -39761,7 +39566,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
     </row>
@@ -39772,7 +39577,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
     </row>
@@ -39949,7 +39754,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D50+F7*(1-변수!D50),"")</f>
+        <f>IFERROR(E7*변수!D49+F7*(1-변수!D49),"")</f>
         <v/>
       </c>
     </row>
@@ -39960,7 +39765,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -39984,7 +39789,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -40008,7 +39813,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -40072,7 +39877,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -40127,7 +39932,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1502.8</v>
+        <v>1499.8</v>
       </c>
     </row>
     <row r="30">
@@ -40147,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.47</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="32">
@@ -40167,7 +39972,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
     </row>
     <row r="34">
@@ -41880,7 +41685,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D57</f>
+        <f>변수!D56</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>26250</v>
+        <v>26200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6168,7 +6168,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>26150</v>
+        <v>26100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>27330</v>
+        <v>27320</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9101,11 +9101,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>26250</v>
+        <v>26200</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,750원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,700원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.2125156653534312</v>
+        <v>0.2125156653534311</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.5</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>26200</v>
+        <v>25200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6168,7 +6168,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>26100</v>
+        <v>25100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>27320</v>
+        <v>26966.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>26200</v>
+        <v>25200</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.47</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="32">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>25200</v>
+        <v>25800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6168,7 +6168,7 @@
         <v>19420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>25100</v>
+        <v>24400</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>26966.7</v>
+        <v>26814.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9101,11 +9101,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>25200</v>
+        <v>25800</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,250원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="32">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>25800</v>
+        <v>27250</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>26814.3</v>
+        <v>26887.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9101,11 +9101,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>25800</v>
+        <v>27250</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,450원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.2</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="32">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -1498,61 +1498,61 @@
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
@@ -1969,37 +1969,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1435억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1437억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1551억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1553억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1667억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1669억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1786억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1788억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1769억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1774억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1894억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +20.63억이 이자손익 추정 +7.99억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 1898억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2029,37 +2029,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1435억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1437억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1551억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1553억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1667억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1669억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1786억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1788억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1769억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1774억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1894억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1898억 × 2.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3110,61 +3110,61 @@
     </comment>
     <comment ref="AC31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AD31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AF31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AG31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AH31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AI31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AK31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AL31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AM31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AN31" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 25,460,640 vs fin 2026Q2 보통주 발행 25,867,242, 비율 0.9843 비정수 감소 — 병합/소각 미확인) − 자기주식 182,971
 [qoq]</t>
       </text>
     </comment>
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 794억(영업이익 72억의 11배, 12분기 중위 55억·기준선 55억) → 지배NI 589억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 335.9원(보고 2,293.6원; 초과 비영업손익 739억 × (1 − 세율 20.4%) × 지배 비중 0.85 = 503억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +20.6억이 이자손익 추정 +8.0억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +278/+141/+280/+791(중위 +279억) → 추정 2026Q3 +8억(차 -271억, -97%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 분기말 후 주식수 감소 비정수: aik 상장주식수 25,460,640 / fin 2026Q2 보통주 발행 25,867,242 = 0.9843 — 병합+소각 복합 가능 → SHARE_EVENTS 수동 확인; 최신 주식수만 25,277,669 로 바꾸고 실적은 환산하지 않음 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 794억(영업이익 72억의 11배, 12분기 중위 55억·기준선 55억) → 지배NI 589억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 335.9원(보고 2,293.6원; 초과 비영업손익 739억 × (1 − 세율 20.4%) × 지배 비중 0.85 = 503억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +20.6억이 이자손익 추정 +8.0억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +278/+141/+280/+791(중위 +279억) → 추정 2026Q3 +8억(차 -271억, -97%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>27250</v>
+        <v>27850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>26887.5</v>
+        <v>26800</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.001426637</v>
+        <v>0.000867756</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.006432463</v>
+        <v>-0.0069374</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.005158254</v>
+        <v>0.004675057</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>137.416409925</v>
+        <v>135.235952194</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.001358742</v>
+        <v>0.00266382</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.002688399</v>
+        <v>-0.001267823</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.003877286</v>
+        <v>-0.002377468</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>137.41489207</v>
+        <v>135.23647534</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.001249449</v>
+        <v>0.002217616</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.000347983</v>
+        <v>-0.006010587</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8065,36 +8065,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.002710044</v>
+        <v>-0.002608776</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.002047167</v>
+        <v>-0.001898473</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.006312485</v>
+        <v>0.006496557</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>137.411845221</v>
+        <v>135.232066727</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.000648768</v>
+        <v>0.001793145</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.001121743</v>
+        <v>0.002370108</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.007415714</v>
+        <v>0.003923067</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>137.413775424</v>
+        <v>135.225206945</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001036902</v>
+        <v>0.001396247</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.003067668</v>
+        <v>-0.000476285</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8419,26 +8419,26 @@
         <v>0.077033324</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>-0.020670265</v>
+        <v>-0.019182607</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.080935126</v>
+        <v>0.080819325</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.07458501200000001</v>
+        <v>0.074486301</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.071123909</v>
+        <v>0.071036156</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.009106642</v>
+        <v>-0.00787036</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.07047618999999999</v>
+        <v>0.070312632</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.06558285899999999</v>
+        <v>0.065445964</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8863,7 +8863,7 @@
         <v/>
       </c>
       <c r="AC39" s="24" t="n">
-        <v>0</v>
+        <v>-0.015820394</v>
       </c>
       <c r="AD39" s="24" t="n">
         <v>0</v>
@@ -9101,11 +9101,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>27250</v>
+        <v>27850</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,850원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.2125156653534311</v>
+        <v>0.2125242315148158</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9239723919637756</v>
+        <v>0.9239784076522719</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02766838073366952</v>
+        <v>0.0276708334312089</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>0.2151</v>
+        <v>0.2117</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39932,7 +39932,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1499.8</v>
+        <v>1523.8</v>
       </c>
     </row>
     <row r="30">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.17</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="32">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="33">
@@ -39972,7 +39972,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0545</v>
+        <v>0.0554</v>
       </c>
     </row>
     <row r="34">
@@ -39982,7 +39982,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="35">
@@ -39992,7 +39992,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/023160_model.xlsx
+++ b/argus/kship/models/023160_model.xlsx
@@ -4140,7 +4140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5018,35 +5018,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5137,35 +5137,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5256,35 +5256,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5375,35 +5375,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5494,35 +5494,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5613,35 +5613,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5732,35 +5732,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5851,35 +5851,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>28150</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>27850</v>
+        <v>24550</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6259,7 +6259,7 @@
         <v>24219.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>26800</v>
+        <v>26540.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9101,11 +9101,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>27850</v>
+        <v>24550</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,500원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.28</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="32">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="33">
